--- a/vignettes/standardisation_outputs/exp1_aov.xlsx
+++ b/vignettes/standardisation_outputs/exp1_aov.xlsx
@@ -454,7 +454,7 @@
         <v>0.4923952707490778</v>
       </c>
       <c r="E5">
-        <v>0.6876326760165989</v>
+        <v>0.6876326760165988</v>
       </c>
     </row>
     <row r="6">
